--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13162,7 +13162,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-02-27T14:45:32.872562+00:00</t>
+    <t>2026-03-02T09:41:45.257476+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13162,7 +13162,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-02T09:41:45.257476+00:00</t>
+    <t>2026-03-02T10:03:43.539775+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13162,7 +13162,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-02T10:03:43.539775+00:00</t>
+    <t>2026-03-02T15:37:52.908313+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13162,7 +13162,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-02T15:37:52.908313+00:00</t>
+    <t>2026-03-03T19:22:12.307473+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -5161,7 +5161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12653" uniqueCount="2587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12653" uniqueCount="2588">
   <si>
     <t>Find potential digital evidence sources</t>
   </si>
@@ -5487,7 +5487,7 @@
     <t>T1043</t>
   </si>
   <si>
-    <t>Decode forensic image format</t>
+    <t>Decode forensic image container format</t>
   </si>
   <si>
     <t>T1044</t>
@@ -10659,7 +10659,7 @@
 T1042</t>
   </si>
   <si>
-    <t>Decode forensic image format
+    <t>Decode forensic image container format
 T1043</t>
   </si>
   <si>
@@ -11741,7 +11741,12 @@
     <t>['Read forensic format', 'Read forensic image']</t>
   </si>
   <si>
-    <t>For example a EWF (Expert Witness Format) needs to be processed to expose the equivalent RAW image sectors. Therefore both the input and output types here are [https://ontology.unifiedcyberontology.org/uco/observable/Image]. This technique would not need to be used when working with a RAW image format directly. This also includes decoding logical formats such as L01, AD1, CTR, or AFF4-L. The output here is not an image file but rather a set of files and their metadata</t>
+    <t>For example a EWF (Expert Witness Format) needs to be processed to expose the equivalent RAW image sectors. 
+This also includes decoding logical formats such as L01, AD1, CTR, or AFF4-L. The output here is not an image file but rather a set of files and their metadata.
+This technique would not need to be used when working with a RAW image format directly.</t>
+  </si>
+  <si>
+    <t>['https://ontology.solveit-df.org/solveit/observable/ForensicImageContainer']</t>
   </si>
   <si>
     <t>['Expert Witness Format (EWF)', 'Advanced Forensic Format (AFF)']</t>
@@ -13282,7 +13287,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-04T01:15:15.680897+00:00</t>
+    <t>2026-03-04T01:15:59.756363+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>
@@ -14394,7 +14399,7 @@
     <hyperlink ref="C4" location="T1011!A1" display="Store seized devices in evidence bags&#10;T1011"/>
     <hyperlink ref="D4" location="T1003!A1" display="Memory imaging&#10;T1003"/>
     <hyperlink ref="E4" location="T1032!A1" display="Side channel&#10;T1032"/>
-    <hyperlink ref="F4" location="T1043!A1" display="Decode forensic image format&#10;T1043"/>
+    <hyperlink ref="F4" location="T1043!A1" display="Decode forensic image container format&#10;T1043"/>
     <hyperlink ref="G4" location="T1047!A1" display="Hash matching (reduce)&#10;T1047"/>
     <hyperlink ref="H4" location="T1060!A1" display="Enumerate allocated files and folders&#10;T1060"/>
     <hyperlink ref="I4" location="T1066!A1" display="Log file examination (OS)&#10;T1066"/>
@@ -15084,7 +15089,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
     </row>
   </sheetData>
@@ -15133,7 +15138,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -15244,7 +15249,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
     </row>
   </sheetData>
@@ -15293,7 +15298,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -15317,7 +15322,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -15341,7 +15346,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -15404,7 +15409,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
     </row>
   </sheetData>
@@ -15453,7 +15458,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -15501,7 +15506,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -15564,7 +15569,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
     </row>
   </sheetData>
@@ -15613,7 +15618,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -15661,7 +15666,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -15724,7 +15729,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
     </row>
   </sheetData>
@@ -15821,7 +15826,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -15970,7 +15975,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -16033,7 +16038,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
     </row>
   </sheetData>
@@ -16082,7 +16087,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -16106,7 +16111,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -16190,18 +16195,18 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="B20" s="10" t="s">
+        <v>2351</v>
+      </c>
+      <c r="I20" s="10" t="s">
         <v>2350</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>2349</v>
       </c>
     </row>
   </sheetData>
@@ -16400,7 +16405,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -16958,7 +16963,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -17155,7 +17160,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -17256,7 +17261,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -17405,7 +17410,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -17554,7 +17559,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -17727,7 +17732,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -17838,7 +17843,7 @@
         <v>1495</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -17848,7 +17853,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="B21" s="10" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>876</v>
@@ -17926,7 +17931,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -17950,7 +17955,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -18121,7 +18126,7 @@
         <v>1931</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -18274,7 +18279,7 @@
         <v>1459</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -18284,10 +18289,10 @@
     </row>
     <row r="23" spans="1:9">
       <c r="B23" s="10" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
     </row>
   </sheetData>
@@ -18378,7 +18383,7 @@
         <v>1931</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -18394,7 +18399,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -18460,7 +18465,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -18489,7 +18494,7 @@
         <v>349</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -18547,7 +18552,7 @@
         <v>349</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -18560,7 +18565,7 @@
         <v>1459</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -18626,7 +18631,7 @@
     </row>
     <row r="31" spans="1:9">
       <c r="B31" s="10" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="I31" s="10" t="s">
         <v>889</v>
@@ -18634,7 +18639,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="B32" s="10" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>889</v>
@@ -18642,7 +18647,7 @@
     </row>
     <row r="33" spans="2:9">
       <c r="B33" s="10" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="I33" s="10" t="s">
         <v>889</v>
@@ -18650,10 +18655,10 @@
     </row>
     <row r="34" spans="2:9">
       <c r="B34" s="10" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
     </row>
   </sheetData>
@@ -18913,7 +18918,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -18921,7 +18926,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -18945,7 +18950,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -19037,7 +19042,7 @@
         <v>2079</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -19045,7 +19050,7 @@
         <v>1979</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
     </row>
   </sheetData>
@@ -19096,7 +19101,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -19152,7 +19157,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -19204,26 +19209,26 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="B20" s="10" t="s">
+        <v>2379</v>
+      </c>
+      <c r="I20" s="10" t="s">
         <v>2378</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>2377</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="B21" s="10" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
     </row>
   </sheetData>
@@ -19274,7 +19279,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -19322,7 +19327,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -19330,7 +19335,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -19396,7 +19401,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -19425,7 +19430,7 @@
         <v>485</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -19509,7 +19514,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="B27" s="10" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>902</v>
@@ -19562,7 +19567,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -19578,7 +19583,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -19610,7 +19615,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -19684,7 +19689,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -19742,7 +19747,7 @@
         <v>349</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -19755,7 +19760,7 @@
         <v>1393</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -19779,7 +19784,7 @@
         <v>1713</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -19787,7 +19792,7 @@
         <v>1718</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -19795,7 +19800,7 @@
         <v>1720</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -19821,10 +19826,10 @@
     </row>
     <row r="30" spans="1:9">
       <c r="B30" s="10" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
     </row>
   </sheetData>
@@ -19878,7 +19883,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -19926,7 +19931,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -19934,7 +19939,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -20081,7 +20086,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="B23" s="10" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>910</v>
@@ -20134,7 +20139,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -20150,7 +20155,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -20182,7 +20187,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -20190,7 +20195,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -20279,7 +20284,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="B21" s="10" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>922</v>
@@ -20287,7 +20292,7 @@
     </row>
     <row r="22" spans="1:9">
       <c r="B22" s="10" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>922</v>
@@ -20357,7 +20362,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -20365,7 +20370,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -20389,7 +20394,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -20397,7 +20402,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -20521,7 +20526,7 @@
         <v>485</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -20534,7 +20539,7 @@
         <v>1495</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -20576,18 +20581,18 @@
     </row>
     <row r="27" spans="1:9">
       <c r="B27" s="10" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="B28" s="10" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
     </row>
   </sheetData>
@@ -20687,7 +20692,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -20761,7 +20766,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -20790,7 +20795,7 @@
         <v>349</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -20819,7 +20824,7 @@
         <v>349</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -20848,7 +20853,7 @@
         <v>349</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -20877,7 +20882,7 @@
         <v>349</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -20898,7 +20903,7 @@
         <v>1212</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -21015,7 +21020,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -21039,7 +21044,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -21047,7 +21052,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -21113,7 +21118,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -21142,7 +21147,7 @@
         <v>349</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -21189,18 +21194,18 @@
     </row>
     <row r="25" spans="1:9">
       <c r="B25" s="10" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="B26" s="10" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
     </row>
   </sheetData>
@@ -21275,7 +21280,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -21299,7 +21304,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -21373,7 +21378,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -21402,7 +21407,7 @@
         <v>349</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -21465,10 +21470,10 @@
     </row>
     <row r="27" spans="1:9">
       <c r="B27" s="10" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
     </row>
   </sheetData>
@@ -21890,7 +21895,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -21922,7 +21927,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -21996,7 +22001,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -22017,7 +22022,7 @@
         <v>1212</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -22027,7 +22032,7 @@
     </row>
     <row r="22" spans="1:9">
       <c r="B22" s="10" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>604</v>
@@ -22097,7 +22102,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -22105,7 +22110,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -22129,7 +22134,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -22216,7 +22221,7 @@
         <v>1536</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -22226,7 +22231,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="B21" s="10" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>944</v>
@@ -22234,7 +22239,7 @@
     </row>
     <row r="22" spans="1:9">
       <c r="B22" s="10" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>944</v>
@@ -22242,7 +22247,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="B23" s="10" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>944</v>
@@ -22314,7 +22319,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -22346,7 +22351,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -22420,7 +22425,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -22449,7 +22454,7 @@
         <v>349</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -22491,7 +22496,7 @@
         <v>1508</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -22499,7 +22504,7 @@
         <v>1511</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -22517,7 +22522,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="B25" s="10" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>928</v>
@@ -22525,7 +22530,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="B26" s="10" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>928</v>
@@ -22597,7 +22602,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -22605,7 +22610,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -22629,7 +22634,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -22726,18 +22731,18 @@
     </row>
     <row r="21" spans="1:9">
       <c r="B21" s="10" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="B22" s="10" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
     </row>
   </sheetData>
@@ -22788,7 +22793,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -22804,7 +22809,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -22812,7 +22817,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -22937,7 +22942,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -23045,18 +23050,18 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="B20" s="10" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
     </row>
   </sheetData>
@@ -23106,7 +23111,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -23130,7 +23135,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -23154,7 +23159,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -23255,7 +23260,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -23303,7 +23308,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -23363,10 +23368,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
     </row>
   </sheetData>
@@ -23415,7 +23420,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -23431,7 +23436,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -23463,7 +23468,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -23523,10 +23528,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
     </row>
   </sheetData>
@@ -23575,7 +23580,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -23599,7 +23604,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -23623,7 +23628,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -23631,7 +23636,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -23697,7 +23702,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -23726,7 +23731,7 @@
         <v>349</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -23755,7 +23760,7 @@
         <v>349</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -23784,7 +23789,7 @@
         <v>349</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -23813,7 +23818,7 @@
         <v>349</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -23842,7 +23847,7 @@
         <v>349</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -23900,7 +23905,7 @@
         <v>349</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -23929,7 +23934,7 @@
         <v>349</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -23958,7 +23963,7 @@
         <v>349</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -23987,7 +23992,7 @@
         <v>349</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -24016,7 +24021,7 @@
         <v>349</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -24074,7 +24079,7 @@
         <v>349</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -24103,7 +24108,7 @@
         <v>349</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -24132,7 +24137,7 @@
         <v>349</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -24161,7 +24166,7 @@
         <v>349</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -24190,7 +24195,7 @@
         <v>349</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -24219,7 +24224,7 @@
         <v>349</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -24248,7 +24253,7 @@
         <v>483</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -24277,7 +24282,7 @@
         <v>349</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -24306,7 +24311,7 @@
         <v>349</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -24335,7 +24340,7 @@
         <v>349</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -24364,7 +24369,7 @@
         <v>349</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -24393,7 +24398,7 @@
         <v>349</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -24422,7 +24427,7 @@
         <v>349</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -24451,7 +24456,7 @@
         <v>349</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -24634,7 +24639,7 @@
     </row>
     <row r="67" spans="1:9">
       <c r="B67" s="10" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="I67" s="10" t="s">
         <v>947</v>
@@ -24642,7 +24647,7 @@
     </row>
     <row r="68" spans="1:9">
       <c r="B68" s="10" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="I68" s="10" t="s">
         <v>947</v>
@@ -24861,7 +24866,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -24869,7 +24874,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -24893,7 +24898,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -24901,7 +24906,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -24967,7 +24972,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -24996,7 +25001,7 @@
         <v>483</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -25054,7 +25059,7 @@
         <v>483</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -25099,7 +25104,7 @@
         <v>1700</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -25125,7 +25130,7 @@
     </row>
     <row r="30" spans="1:9">
       <c r="B30" s="10" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="I30" s="10" t="s">
         <v>1060</v>
@@ -25195,7 +25200,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -25203,7 +25208,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -25227,7 +25232,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -25301,7 +25306,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -25359,7 +25364,7 @@
         <v>349</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -25417,7 +25422,7 @@
         <v>485</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -25554,7 +25559,7 @@
         <v>1302</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -25562,7 +25567,7 @@
         <v>1636</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -25586,7 +25591,7 @@
         <v>1645</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -25596,15 +25601,15 @@
     </row>
     <row r="34" spans="1:9">
       <c r="B34" s="10" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="B35" s="10" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>1301</v>
@@ -25612,18 +25617,18 @@
     </row>
     <row r="36" spans="1:9">
       <c r="B36" s="10" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="B37" s="10" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
     </row>
   </sheetData>
@@ -25695,7 +25700,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -25727,7 +25732,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -25824,10 +25829,10 @@
     </row>
     <row r="21" spans="1:9">
       <c r="B21" s="10" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
     </row>
   </sheetData>
@@ -26223,7 +26228,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -26402,7 +26407,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -26581,7 +26586,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -26817,7 +26822,7 @@
         <v>1633</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -26827,10 +26832,10 @@
     </row>
     <row r="21" spans="1:9">
       <c r="B21" s="10" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
   </sheetData>
@@ -27227,7 +27232,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -27376,7 +27381,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -27493,7 +27498,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -27501,7 +27506,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -27585,10 +27590,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
     </row>
   </sheetData>
@@ -27637,7 +27642,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -27653,7 +27658,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -27661,7 +27666,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -27685,7 +27690,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -27693,7 +27698,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -27745,34 +27750,34 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="B20" s="10" t="s">
+        <v>2513</v>
+      </c>
+      <c r="I20" s="10" t="s">
         <v>2512</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>2511</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="B21" s="10" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="B22" s="10" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
     </row>
   </sheetData>
@@ -27872,7 +27877,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -27946,7 +27951,7 @@
         <v>485</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -27975,7 +27980,7 @@
         <v>485</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -28004,7 +28009,7 @@
         <v>485</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -28033,7 +28038,7 @@
         <v>349</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -28062,7 +28067,7 @@
         <v>349</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -28091,7 +28096,7 @@
         <v>485</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -28186,15 +28191,15 @@
     </row>
     <row r="35" spans="1:9">
       <c r="B35" s="10" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="B36" s="10" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="I36" s="10" t="s">
         <v>787</v>
@@ -28264,7 +28269,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -28272,7 +28277,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -28296,7 +28301,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -28304,7 +28309,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -28370,7 +28375,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -28383,7 +28388,7 @@
         <v>1659</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -28391,7 +28396,7 @@
         <v>1662</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -28401,7 +28406,7 @@
     </row>
     <row r="22" spans="1:9">
       <c r="B22" s="10" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>1053</v>
@@ -28480,7 +28485,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -28504,7 +28509,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -28578,7 +28583,7 @@
         <v>483</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -28694,7 +28699,7 @@
         <v>1713</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -28712,10 +28717,10 @@
     </row>
     <row r="27" spans="1:9">
       <c r="B27" s="10" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
     </row>
   </sheetData>
@@ -28766,7 +28771,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -28782,7 +28787,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -28814,7 +28819,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -28874,18 +28879,18 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="B20" s="10" t="s">
+        <v>2536</v>
+      </c>
+      <c r="I20" s="10" t="s">
         <v>2535</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>2534</v>
       </c>
     </row>
   </sheetData>
@@ -28935,7 +28940,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -28951,7 +28956,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -28959,7 +28964,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -28983,7 +28988,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -29084,7 +29089,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -29108,7 +29113,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -29132,7 +29137,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -29521,7 +29526,7 @@
         <v>1930</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -29537,7 +29542,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -29545,7 +29550,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -29827,18 +29832,18 @@
     </row>
     <row r="32" spans="1:9">
       <c r="B32" s="10" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="33" spans="2:9">
       <c r="B33" s="10" t="s">
+        <v>2547</v>
+      </c>
+      <c r="I33" s="10" t="s">
         <v>2546</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>2545</v>
       </c>
     </row>
     <row r="34" spans="2:9">
@@ -29846,7 +29851,7 @@
         <v>2001</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
     </row>
   </sheetData>
@@ -29955,7 +29960,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -30021,7 +30026,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -30066,7 +30071,7 @@
         <v>1749</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -30074,7 +30079,7 @@
         <v>1752</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -30084,18 +30089,18 @@
     </row>
     <row r="26" spans="1:9">
       <c r="B26" s="10" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="B27" s="10" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
     </row>
   </sheetData>
@@ -30176,7 +30181,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -30208,7 +30213,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -30297,7 +30302,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="B21" s="10" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>1096</v>
@@ -30305,7 +30310,7 @@
     </row>
     <row r="22" spans="1:9">
       <c r="B22" s="10" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>1096</v>
@@ -30316,7 +30321,7 @@
         <v>2034</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
     </row>
   </sheetData>
@@ -30416,7 +30421,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -30476,10 +30481,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
     </row>
   </sheetData>
@@ -30544,7 +30549,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -30560,7 +30565,7 @@
         <v>1930</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -30576,7 +30581,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -30636,10 +30641,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
     </row>
   </sheetData>
@@ -30736,7 +30741,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -30796,18 +30801,18 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="B20" s="10" t="s">
+        <v>2571</v>
+      </c>
+      <c r="I20" s="10" t="s">
         <v>2570</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>2569</v>
       </c>
     </row>
   </sheetData>
@@ -30881,7 +30886,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -30897,7 +30902,7 @@
         <v>1931</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2572</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -31094,7 +31099,7 @@
         <v>1931</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -31102,7 +31107,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -31176,7 +31181,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -31197,7 +31202,7 @@
         <v>1754</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -31824,23 +31829,23 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="B1" t="s">
-        <v>2578</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
       <c r="B2" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="B3">
         <v>19</v>
@@ -31848,7 +31853,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="B4">
         <v>161</v>
@@ -31856,7 +31861,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
       <c r="B5">
         <v>271</v>
@@ -31864,7 +31869,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
       <c r="B6">
         <v>234</v>
@@ -31872,7 +31877,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="B7">
         <v>72</v>
@@ -31880,7 +31885,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>2586</v>
+        <v>2587</v>
       </c>
       <c r="B8">
         <v>0.45</v>
@@ -43036,7 +43041,7 @@
         <v>1931</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>825</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -43044,7 +43049,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2039</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -43052,7 +43057,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -43205,7 +43210,7 @@
         <v>349</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -43284,15 +43289,15 @@
     </row>
     <row r="31" spans="1:9">
       <c r="B31" s="10" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="B32" s="10" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>757</v>
@@ -43303,7 +43308,7 @@
         <v>2122</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
     </row>
   </sheetData>
@@ -48464,7 +48469,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -48538,7 +48543,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -48567,7 +48572,7 @@
         <v>349</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -48596,7 +48601,7 @@
         <v>349</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -48625,7 +48630,7 @@
         <v>349</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -48823,7 +48828,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -48897,7 +48902,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -48978,7 +48983,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -49026,7 +49031,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -49127,7 +49132,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -49175,7 +49180,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -49267,7 +49272,7 @@
         <v>2023</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -49275,7 +49280,7 @@
         <v>2122</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
     </row>
   </sheetData>
@@ -49326,7 +49331,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -49350,7 +49355,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -49374,7 +49379,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -49434,10 +49439,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
     </row>
   </sheetData>
@@ -49486,7 +49491,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -49502,7 +49507,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -49510,7 +49515,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -49518,7 +49523,7 @@
         <v>1930</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -49534,7 +49539,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -49608,7 +49613,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -49666,7 +49671,7 @@
         <v>349</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -49766,15 +49771,15 @@
     </row>
     <row r="30" spans="1:9">
       <c r="B30" s="10" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="B31" s="10" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="I31" s="10" t="s">
         <v>607</v>
@@ -49782,7 +49787,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="B32" s="10" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>607</v>
@@ -49790,10 +49795,10 @@
     </row>
     <row r="33" spans="2:9">
       <c r="B33" s="10" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
     </row>
   </sheetData>
@@ -49846,7 +49851,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -49894,7 +49899,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -49986,7 +49991,7 @@
         <v>2023</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -49994,7 +49999,7 @@
         <v>2122</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
     </row>
   </sheetData>
@@ -50045,7 +50050,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -50093,7 +50098,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -50156,7 +50161,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
     </row>
   </sheetData>
@@ -50221,7 +50226,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -50237,7 +50242,7 @@
         <v>1930</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -50253,7 +50258,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -50261,7 +50266,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -50485,7 +50490,7 @@
         <v>1393</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -50495,7 +50500,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="B26" s="10" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>810</v>
@@ -50503,10 +50508,10 @@
     </row>
     <row r="27" spans="1:9">
       <c r="B27" s="10" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
     </row>
   </sheetData>
@@ -50669,7 +50674,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
     </row>
   </sheetData>
@@ -54723,7 +54728,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -54747,7 +54752,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -54771,7 +54776,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -54845,7 +54850,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -54874,7 +54879,7 @@
         <v>349</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -54903,7 +54908,7 @@
         <v>349</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -54992,7 +54997,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -55103,7 +55108,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
     </row>
   </sheetData>
@@ -55200,7 +55205,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -55263,7 +55268,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
     </row>
   </sheetData>
@@ -55312,7 +55317,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -55360,7 +55365,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -55420,10 +55425,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
     </row>
   </sheetData>
@@ -55472,7 +55477,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -55496,7 +55501,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -55520,7 +55525,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -55580,10 +55585,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
     </row>
   </sheetData>
@@ -55632,7 +55637,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -55648,7 +55653,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -55656,7 +55661,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -55680,7 +55685,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -55688,7 +55693,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -55754,7 +55759,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -55783,7 +55788,7 @@
         <v>349</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -55841,7 +55846,7 @@
         <v>349</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -55870,7 +55875,7 @@
         <v>349</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -55957,7 +55962,7 @@
     </row>
     <row r="33" spans="2:9">
       <c r="B33" s="10" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="I33" s="10" t="s">
         <v>632</v>
@@ -55965,7 +55970,7 @@
     </row>
     <row r="34" spans="2:9">
       <c r="B34" s="10" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="I34" s="10" t="s">
         <v>632</v>
@@ -55973,7 +55978,7 @@
     </row>
     <row r="35" spans="2:9">
       <c r="B35" s="10" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>1243</v>
@@ -55989,7 +55994,7 @@
     </row>
     <row r="37" spans="2:9">
       <c r="B37" s="10" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="I37" s="10" t="s">
         <v>1238</v>
@@ -55997,10 +56002,10 @@
     </row>
     <row r="38" spans="2:9">
       <c r="B38" s="10" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
     </row>
   </sheetData>
@@ -56055,7 +56060,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -56071,7 +56076,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -56103,7 +56108,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -56111,7 +56116,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -56177,7 +56182,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -56206,7 +56211,7 @@
         <v>349</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -56235,7 +56240,7 @@
         <v>349</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -56264,7 +56269,7 @@
         <v>349</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -56293,7 +56298,7 @@
         <v>349</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -56322,7 +56327,7 @@
         <v>349</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -56351,7 +56356,7 @@
         <v>349</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -56380,7 +56385,7 @@
         <v>349</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -56409,7 +56414,7 @@
         <v>349</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -56438,7 +56443,7 @@
         <v>485</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -56467,7 +56472,7 @@
         <v>485</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -56496,7 +56501,7 @@
         <v>349</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -56525,7 +56530,7 @@
         <v>349</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -56554,7 +56559,7 @@
         <v>349</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -56583,7 +56588,7 @@
         <v>349</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -56612,7 +56617,7 @@
         <v>349</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -56641,7 +56646,7 @@
         <v>349</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -56688,7 +56693,7 @@
     </row>
     <row r="40" spans="1:9">
       <c r="B40" s="10" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="I40" s="10" t="s">
         <v>643</v>
@@ -56696,7 +56701,7 @@
     </row>
     <row r="41" spans="1:9">
       <c r="B41" s="10" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="I41" s="10" t="s">
         <v>643</v>
@@ -56750,7 +56755,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -56766,7 +56771,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -56782,7 +56787,7 @@
         <v>1930</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -56798,7 +56803,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -56895,10 +56900,10 @@
     </row>
     <row r="21" spans="1:9">
       <c r="B21" s="10" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -56957,7 +56962,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -56981,7 +56986,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -57005,7 +57010,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -57068,7 +57073,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
     </row>
   </sheetData>
@@ -57117,7 +57122,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -57141,7 +57146,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -57165,7 +57170,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -57239,7 +57244,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -57268,7 +57273,7 @@
         <v>349</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -57297,7 +57302,7 @@
         <v>349</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -57344,7 +57349,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="B26" s="10" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>774</v>
@@ -57355,39 +57360,39 @@
         <v>2122</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="B28" s="10" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="B29" s="10" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="B30" s="10" t="s">
+        <v>2225</v>
+      </c>
+      <c r="I30" s="10" t="s">
         <v>2224</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>2223</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="B31" s="10" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
     </row>
   </sheetData>
@@ -57749,7 +57754,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -57773,7 +57778,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -57781,7 +57786,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -57876,7 +57881,7 @@
         <v>349</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -57905,7 +57910,7 @@
         <v>349</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -57963,7 +57968,7 @@
         <v>349</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -57976,7 +57981,7 @@
         <v>1284</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -58042,7 +58047,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="B32" s="10" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>715</v>
@@ -58050,7 +58055,7 @@
     </row>
     <row r="33" spans="2:9">
       <c r="B33" s="10" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="I33" s="10" t="s">
         <v>715</v>
@@ -58058,10 +58063,10 @@
     </row>
     <row r="34" spans="2:9">
       <c r="B34" s="10" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
     </row>
   </sheetData>
@@ -58114,7 +58119,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -58138,7 +58143,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -58162,7 +58167,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -58170,7 +58175,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -58222,18 +58227,18 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="B20" s="10" t="s">
+        <v>2243</v>
+      </c>
+      <c r="I20" s="10" t="s">
         <v>2242</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>2241</v>
       </c>
     </row>
   </sheetData>
@@ -58283,7 +58288,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -58331,7 +58336,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -58394,7 +58399,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
     </row>
   </sheetData>
@@ -58443,7 +58448,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -58554,7 +58559,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
     </row>
   </sheetData>
@@ -58603,7 +58608,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -58627,7 +58632,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -58651,7 +58656,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -58714,7 +58719,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
     </row>
   </sheetData>
@@ -58763,7 +58768,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -58787,7 +58792,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -58795,7 +58800,7 @@
         <v>1930</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -58811,7 +58816,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -58956,7 +58961,7 @@
         <v>1621</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -58964,7 +58969,7 @@
         <v>1624</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -58982,7 +58987,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="B25" s="10" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>737</v>
@@ -58990,7 +58995,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="B26" s="10" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>737</v>
@@ -59046,7 +59051,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -59094,7 +59099,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -59211,7 +59216,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -59243,7 +59248,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -59251,7 +59256,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -59317,7 +59322,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -59346,7 +59351,7 @@
         <v>485</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -59499,7 +59504,7 @@
         <v>1446</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -59541,7 +59546,7 @@
     </row>
     <row r="33" spans="2:9">
       <c r="B33" s="10" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="I33" s="10" t="s">
         <v>863</v>
@@ -59549,26 +59554,26 @@
     </row>
     <row r="34" spans="2:9">
       <c r="B34" s="10" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="35" spans="2:9">
       <c r="B35" s="10" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="36" spans="2:9">
       <c r="B36" s="10" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
     </row>
   </sheetData>
@@ -59622,7 +59627,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -59638,7 +59643,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -59646,7 +59651,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -59670,7 +59675,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -59744,7 +59749,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -59773,7 +59778,7 @@
         <v>349</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -59802,7 +59807,7 @@
         <v>349</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -59831,7 +59836,7 @@
         <v>349</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -59860,7 +59865,7 @@
         <v>349</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -59889,7 +59894,7 @@
         <v>349</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -59918,7 +59923,7 @@
         <v>349</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -59947,7 +59952,7 @@
         <v>349</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -59976,7 +59981,7 @@
         <v>485</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -60005,7 +60010,7 @@
         <v>349</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -60034,7 +60039,7 @@
         <v>349</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -60063,7 +60068,7 @@
         <v>349</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -60092,7 +60097,7 @@
         <v>349</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -60121,7 +60126,7 @@
         <v>349</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -60150,7 +60155,7 @@
         <v>349</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -60179,7 +60184,7 @@
         <v>349</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -60208,7 +60213,7 @@
         <v>349</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -60237,7 +60242,7 @@
         <v>485</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -60300,26 +60305,26 @@
     </row>
     <row r="43" spans="1:9">
       <c r="B43" s="10" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="B44" s="10" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="B45" s="10" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
     </row>
   </sheetData>
@@ -60371,7 +60376,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -60419,7 +60424,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -61036,7 +61041,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -61185,7 +61190,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -61358,7 +61363,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -61382,7 +61387,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -61390,7 +61395,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -61456,7 +61461,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -61514,7 +61519,7 @@
         <v>349</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -61572,7 +61577,7 @@
         <v>349</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -61630,7 +61635,7 @@
         <v>483</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -61659,7 +61664,7 @@
         <v>349</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -61799,10 +61804,10 @@
     </row>
     <row r="40" spans="1:9">
       <c r="B40" s="10" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
     </row>
   </sheetData>
@@ -61852,7 +61857,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -62001,7 +62006,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -62150,7 +62155,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -62261,7 +62266,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
     </row>
   </sheetData>
@@ -62310,7 +62315,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -62342,7 +62347,7 @@
         <v>1930</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -62421,7 +62426,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
     </row>
   </sheetData>
@@ -62470,7 +62475,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -62581,7 +62586,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
     </row>
   </sheetData>
@@ -62630,7 +62635,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -62741,7 +62746,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
     </row>
   </sheetData>
@@ -62790,7 +62795,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -63359,7 +63364,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -63470,7 +63475,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
     </row>
   </sheetData>
@@ -63519,7 +63524,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -63630,7 +63635,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
     </row>
   </sheetData>
@@ -63679,7 +63684,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -63695,7 +63700,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -63703,7 +63708,7 @@
         <v>1928</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -63711,7 +63716,7 @@
         <v>1930</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -63727,7 +63732,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -63735,7 +63740,7 @@
         <v>1935</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -63801,7 +63806,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -63830,7 +63835,7 @@
         <v>349</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -63843,7 +63848,7 @@
         <v>1393</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -63859,7 +63864,7 @@
         <v>1713</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -63867,7 +63872,7 @@
         <v>1718</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -63875,7 +63880,7 @@
         <v>1720</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -63901,42 +63906,42 @@
     </row>
     <row r="28" spans="1:9">
       <c r="B28" s="10" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="B29" s="10" t="s">
+        <v>2315</v>
+      </c>
+      <c r="I29" s="10" t="s">
         <v>2314</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>2313</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="B30" s="10" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="B31" s="10" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="B32" s="10" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
     </row>
   </sheetData>
@@ -63994,7 +63999,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -64042,7 +64047,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -64143,7 +64148,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -64159,7 +64164,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -64191,7 +64196,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -64251,10 +64256,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
     </row>
   </sheetData>
@@ -64303,7 +64308,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -64414,7 +64419,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
     </row>
   </sheetData>
@@ -64463,7 +64468,7 @@
         <v>1924</v>
       </c>
       <c r="B3" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -64574,7 +64579,7 @@
         <v>2023</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
     </row>
   </sheetData>
@@ -64639,7 +64644,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -64671,7 +64676,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -64847,7 +64852,7 @@
         <v>1927</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -64879,7 +64884,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -64953,7 +64958,7 @@
         <v>349</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -64982,7 +64987,7 @@
         <v>349</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -65066,7 +65071,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="B27" s="10" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>830</v>
@@ -65074,7 +65079,7 @@
     </row>
     <row r="28" spans="1:9">
       <c r="B28" s="10" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>830</v>
@@ -65176,7 +65181,7 @@
         <v>1933</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="10" spans="1:10">

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -5159,7 +5159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13032" uniqueCount="2657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13032" uniqueCount="2656">
   <si>
     <t>Prepare for a digital investigation</t>
   </si>
@@ -11336,10 +11336,6 @@
   </si>
   <si>
     <t>['https://ontology.unifiedcyberontology.org/uco/observable/Memory']</t>
-  </si>
-  <si>
-    <t>['https://ontology.solveit-df.org/solveit/observable/RawImage',
- 'https://ontology.solveit-df.org/solveit/observable/RawImageInfoFile']</t>
   </si>
   <si>
     <t>['FTK Imager']</t>
@@ -11778,6 +11774,9 @@
   </si>
   <si>
     <t>M1094, M1095, M1097, M1231</t>
+  </si>
+  <si>
+    <t>Use a brute force attack instead (T1034)</t>
   </si>
   <si>
     <t>Kanta, A., Coisel, I. and Scanlon, M., 2021, December. PCWQ: A framework for evaluating password cracking wordlist quality. In International Conference on Digital Forensics and Cyber Crime (pp. 159-175). Cham: Springer International Publishing.</t>
@@ -12657,7 +12656,7 @@
   </si>
   <si>
     <t>['https://ontology.unifiedcyberontology.org/uco/observable/systemTime',
- 'https://ontology.solveit-df.org/solveit/observable/ClockOffset']</t>
+ 'https://ontology.solveit-df.org/solveit/observable/ClockOffsetCapture']</t>
   </si>
   <si>
     <t>['https://ontology.unifiedcyberontology.org/uco/observable/Computer']</t>
@@ -13016,9 +13015,6 @@
     <t>Correlate timestamps from the system clock and an external trusted source of time contained in the same artifact, allowing an offset to be estimated *for the point in time the timestamp was recorded*</t>
   </si>
   <si>
-    <t>['https://ontology.solveit-df.org/solveit/observable/ClockOffset']</t>
-  </si>
-  <si>
     <t>['Browser caches often contain local timestamps and those derived from '
  'external servers',
  'Records in web browser history databases contain local timestamps and, in '
@@ -13468,7 +13464,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-05T15:03:35.299661+00:00</t>
+    <t>2026-03-05T19:10:06.448943+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>
@@ -14820,7 +14816,7 @@
         <v>1964</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -14828,7 +14824,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -14844,7 +14840,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -14852,7 +14848,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -14860,7 +14856,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -15204,7 +15200,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -15312,7 +15308,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2380</v>
@@ -15472,7 +15468,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2381</v>
@@ -15632,7 +15628,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2384</v>
@@ -15792,7 +15788,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2386</v>
@@ -15952,7 +15948,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2388</v>
@@ -16004,7 +16000,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -16153,7 +16149,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -16261,7 +16257,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2391</v>
@@ -16780,7 +16776,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -16796,7 +16792,7 @@
         <v>1964</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -16804,7 +16800,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -16828,7 +16824,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -16902,7 +16898,7 @@
         <v>368</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -16915,7 +16911,7 @@
         <v>1332</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -16923,7 +16919,7 @@
         <v>1335</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -16949,7 +16945,7 @@
     </row>
     <row r="24" spans="1:9">
       <c r="B24" s="10" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>768</v>
@@ -16957,7 +16953,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="B25" s="10" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>768</v>
@@ -16965,26 +16961,26 @@
     </row>
     <row r="26" spans="1:9">
       <c r="B26" s="10" t="s">
+        <v>2034</v>
+      </c>
+      <c r="I26" s="10" t="s">
         <v>2035</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>2036</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="B27" s="10" t="s">
+        <v>2036</v>
+      </c>
+      <c r="I27" s="10" t="s">
         <v>2037</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>2038</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="B28" s="10" t="s">
+        <v>2038</v>
+      </c>
+      <c r="I28" s="10" t="s">
         <v>2039</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>2040</v>
       </c>
     </row>
   </sheetData>
@@ -17934,7 +17930,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -18360,7 +18356,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -18617,7 +18613,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -18938,7 +18934,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -18954,7 +18950,7 @@
         <v>1964</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -18986,7 +18982,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -19075,7 +19071,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="B20" s="10" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>524</v>
@@ -19265,7 +19261,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="B20" s="10" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>2418</v>
@@ -19273,7 +19269,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="B21" s="10" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>2419</v>
@@ -19685,7 +19681,7 @@
         <v>368</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -20149,7 +20145,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20572,7 +20568,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -21749,7 +21745,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -21797,7 +21793,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -21805,7 +21801,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -21871,7 +21867,7 @@
         <v>368</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -21958,7 +21954,7 @@
         <v>368</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -22050,7 +22046,7 @@
     </row>
     <row r="30" spans="1:9">
       <c r="B30" s="10" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="I30" s="10" t="s">
         <v>531</v>
@@ -24927,7 +24923,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -25124,7 +25120,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2514</v>
+        <v>853</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -25132,7 +25128,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -25198,7 +25194,7 @@
         <v>368</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -25227,7 +25223,7 @@
         <v>512</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -25285,7 +25281,7 @@
         <v>512</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -25330,7 +25326,7 @@
         <v>1728</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -25426,7 +25422,7 @@
         <v>1964</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -25434,7 +25430,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -25458,7 +25454,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -25466,7 +25462,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -25532,7 +25528,7 @@
         <v>368</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -25590,7 +25586,7 @@
         <v>368</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -25648,7 +25644,7 @@
         <v>514</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -25785,7 +25781,7 @@
         <v>1330</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -25793,7 +25789,7 @@
         <v>1664</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -25817,7 +25813,7 @@
         <v>1673</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -25827,15 +25823,15 @@
     </row>
     <row r="34" spans="1:9">
       <c r="B34" s="10" t="s">
+        <v>2529</v>
+      </c>
+      <c r="I34" s="10" t="s">
         <v>2530</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>2531</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="B35" s="10" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>1329</v>
@@ -25843,18 +25839,18 @@
     </row>
     <row r="36" spans="1:9">
       <c r="B36" s="10" t="s">
+        <v>2532</v>
+      </c>
+      <c r="I36" s="10" t="s">
         <v>2533</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>2534</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="B37" s="10" t="s">
+        <v>2534</v>
+      </c>
+      <c r="I37" s="10" t="s">
         <v>2535</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>2536</v>
       </c>
     </row>
   </sheetData>
@@ -25926,7 +25922,7 @@
         <v>1964</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -25950,7 +25946,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -25958,7 +25954,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -26055,10 +26051,10 @@
     </row>
     <row r="21" spans="1:9">
       <c r="B21" s="10" t="s">
+        <v>2539</v>
+      </c>
+      <c r="I21" s="10" t="s">
         <v>2540</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>2541</v>
       </c>
     </row>
   </sheetData>
@@ -26454,7 +26450,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -26633,7 +26629,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -26812,7 +26808,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -27048,7 +27044,7 @@
         <v>1661</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -27058,10 +27054,10 @@
     </row>
     <row r="21" spans="1:9">
       <c r="B21" s="10" t="s">
+        <v>2545</v>
+      </c>
+      <c r="I21" s="10" t="s">
         <v>2546</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>2547</v>
       </c>
     </row>
   </sheetData>
@@ -27261,7 +27257,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -27458,7 +27454,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -27607,7 +27603,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -27724,7 +27720,7 @@
         <v>1964</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -27732,7 +27728,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -27816,10 +27812,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
+        <v>2550</v>
+      </c>
+      <c r="I19" s="10" t="s">
         <v>2551</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>2552</v>
       </c>
     </row>
   </sheetData>
@@ -27884,7 +27880,7 @@
         <v>1964</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -27892,7 +27888,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -27916,7 +27912,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -27924,7 +27920,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -27976,34 +27972,34 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
+        <v>2556</v>
+      </c>
+      <c r="I19" s="10" t="s">
         <v>2557</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>2558</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="B20" s="10" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="B21" s="10" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="B22" s="10" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
     </row>
   </sheetData>
@@ -28177,7 +28173,7 @@
         <v>514</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2562</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -28206,7 +28202,7 @@
         <v>514</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2562</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -28235,7 +28231,7 @@
         <v>514</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2563</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -28264,7 +28260,7 @@
         <v>368</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>2564</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -28293,7 +28289,7 @@
         <v>368</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -28322,7 +28318,7 @@
         <v>514</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -28420,7 +28416,7 @@
         <v>2249</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -28495,7 +28491,7 @@
         <v>1964</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2568</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -28503,7 +28499,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -28535,7 +28531,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -28601,7 +28597,7 @@
         <v>368</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -28614,7 +28610,7 @@
         <v>1687</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -28622,7 +28618,7 @@
         <v>1690</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>2573</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -28632,7 +28628,7 @@
     </row>
     <row r="22" spans="1:9">
       <c r="B22" s="10" t="s">
-        <v>2574</v>
+        <v>2573</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>1081</v>
@@ -28711,7 +28707,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2575</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -28735,7 +28731,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2576</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -28809,7 +28805,7 @@
         <v>512</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2577</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -29013,7 +29009,7 @@
         <v>1964</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2578</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -29045,7 +29041,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -29105,18 +29101,18 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
+        <v>2579</v>
+      </c>
+      <c r="I19" s="10" t="s">
         <v>2580</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>2581</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="B20" s="10" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
     </row>
   </sheetData>
@@ -29182,7 +29178,7 @@
         <v>1964</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2583</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -29190,7 +29186,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -29214,7 +29210,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -29339,7 +29335,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -29363,7 +29359,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2587</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -29464,7 +29460,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -29488,7 +29484,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -29667,10 +29663,10 @@
     </row>
     <row r="23" spans="1:9">
       <c r="B23" s="10" t="s">
+        <v>2048</v>
+      </c>
+      <c r="I23" s="10" t="s">
         <v>2049</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>2050</v>
       </c>
     </row>
   </sheetData>
@@ -29752,7 +29748,7 @@
         <v>1967</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -29760,7 +29756,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -29768,7 +29764,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -29776,7 +29772,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2590</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -29842,7 +29838,7 @@
         <v>512</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -29900,7 +29896,7 @@
         <v>368</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -30024,7 +30020,7 @@
         <v>1194</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -30058,26 +30054,26 @@
     </row>
     <row r="32" spans="1:9">
       <c r="B32" s="10" t="s">
+        <v>2590</v>
+      </c>
+      <c r="I32" s="10" t="s">
         <v>2591</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>2592</v>
       </c>
     </row>
     <row r="33" spans="2:9">
       <c r="B33" s="10" t="s">
-        <v>2593</v>
+        <v>2592</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>2592</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="34" spans="2:9">
       <c r="B34" s="10" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
     </row>
   </sheetData>
@@ -30130,7 +30126,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -30186,7 +30182,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -30252,7 +30248,7 @@
         <v>368</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2596</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -30265,7 +30261,7 @@
         <v>1409</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -30273,7 +30269,7 @@
         <v>1766</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -30281,7 +30277,7 @@
         <v>1770</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -30289,7 +30285,7 @@
         <v>1772</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -30297,7 +30293,7 @@
         <v>1777</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -30305,7 +30301,7 @@
         <v>1780</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>2598</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -30315,18 +30311,18 @@
     </row>
     <row r="26" spans="1:9">
       <c r="B26" s="10" t="s">
-        <v>2593</v>
+        <v>2592</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>2599</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="B27" s="10" t="s">
+        <v>2599</v>
+      </c>
+      <c r="I27" s="10" t="s">
         <v>2600</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>2601</v>
       </c>
     </row>
   </sheetData>
@@ -30407,7 +30403,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2602</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -30423,7 +30419,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -30431,7 +30427,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -30439,7 +30435,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2603</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -30528,7 +30524,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="B21" s="10" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>1124</v>
@@ -30536,7 +30532,7 @@
     </row>
     <row r="22" spans="1:9">
       <c r="B22" s="10" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>1124</v>
@@ -30544,10 +30540,10 @@
     </row>
     <row r="23" spans="1:9">
       <c r="B23" s="10" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
     </row>
   </sheetData>
@@ -30647,7 +30643,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -30707,10 +30703,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
+        <v>2607</v>
+      </c>
+      <c r="I19" s="10" t="s">
         <v>2608</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>2609</v>
       </c>
     </row>
   </sheetData>
@@ -30775,7 +30771,7 @@
         <v>1964</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2610</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -30791,7 +30787,7 @@
         <v>1967</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -30867,10 +30863,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
+        <v>2611</v>
+      </c>
+      <c r="I19" s="10" t="s">
         <v>2612</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>2613</v>
       </c>
     </row>
   </sheetData>
@@ -30959,7 +30955,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -30967,7 +30963,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -31027,18 +31023,18 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
+        <v>2613</v>
+      </c>
+      <c r="I19" s="10" t="s">
         <v>2614</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>2615</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="B20" s="10" t="s">
-        <v>2616</v>
+        <v>2615</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
     </row>
   </sheetData>
@@ -31112,7 +31108,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2617</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -31128,7 +31124,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -31277,7 +31273,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -31285,7 +31281,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -31359,7 +31355,7 @@
         <v>368</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -31380,7 +31376,7 @@
         <v>1782</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -31434,7 +31430,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -31458,7 +31454,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -31474,7 +31470,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -31482,7 +31478,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -31490,7 +31486,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -31542,10 +31538,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
+        <v>2626</v>
+      </c>
+      <c r="I19" s="10" t="s">
         <v>2627</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>2628</v>
       </c>
     </row>
   </sheetData>
@@ -31634,7 +31630,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -31743,7 +31739,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -31892,7 +31888,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -31916,7 +31912,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2630</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -31932,7 +31928,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -32057,7 +32053,7 @@
         <v>1964</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2631</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -32081,7 +32077,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -32089,7 +32085,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -32097,7 +32093,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -32152,15 +32148,15 @@
         <v>2175</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="B20" s="10" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
     </row>
   </sheetData>
@@ -32258,7 +32254,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -32375,7 +32371,7 @@
         <v>1964</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -32383,7 +32379,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2637</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -32399,7 +32395,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -32532,7 +32528,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -32548,7 +32544,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -32556,7 +32552,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -32681,7 +32677,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -32697,7 +32693,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -32705,7 +32701,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -32846,7 +32842,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -32854,7 +32850,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -32914,10 +32910,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
+        <v>2644</v>
+      </c>
+      <c r="I19" s="10" t="s">
         <v>2645</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>2646</v>
       </c>
     </row>
   </sheetData>
@@ -32966,7 +32962,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -32990,7 +32986,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -33006,7 +33002,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -33014,7 +33010,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -33088,7 +33084,7 @@
         <v>368</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -33201,10 +33197,10 @@
     </row>
     <row r="27" spans="1:9">
       <c r="B27" s="10" t="s">
+        <v>2054</v>
+      </c>
+      <c r="I27" s="10" t="s">
         <v>2055</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>2056</v>
       </c>
     </row>
   </sheetData>
@@ -33254,7 +33250,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -33294,7 +33290,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -33302,7 +33298,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -33362,10 +33358,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
+        <v>2057</v>
+      </c>
+      <c r="I19" s="10" t="s">
         <v>2058</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>2059</v>
       </c>
     </row>
   </sheetData>
@@ -33390,23 +33386,23 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>2646</v>
+      </c>
+      <c r="B1" t="s">
         <v>2647</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2648</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>2648</v>
+      </c>
+      <c r="B2" t="s">
         <v>2649</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2650</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="B3">
         <v>20</v>
@@ -33414,7 +33410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="B4">
         <v>170</v>
@@ -33422,7 +33418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="B5">
         <v>271</v>
@@ -33430,7 +33426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="B6">
         <v>234</v>
@@ -33438,7 +33434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>2655</v>
+        <v>2654</v>
       </c>
       <c r="B7">
         <v>71</v>
@@ -33446,7 +33442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>2656</v>
+        <v>2655</v>
       </c>
       <c r="B8">
         <v>0.42</v>
@@ -33492,7 +33488,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -33600,10 +33596,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
+        <v>2060</v>
+      </c>
+      <c r="I19" s="10" t="s">
         <v>2061</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>2062</v>
       </c>
     </row>
   </sheetData>
@@ -33708,7 +33704,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -33774,7 +33770,7 @@
         <v>368</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -33861,7 +33857,7 @@
         <v>368</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -33900,7 +33896,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="B26" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>568</v>
@@ -33969,7 +33965,7 @@
         <v>1964</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -33977,7 +33973,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -34001,7 +33997,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -34009,7 +34005,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -34133,7 +34129,7 @@
         <v>368</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -34172,7 +34168,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="B25" s="10" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>589</v>
@@ -34180,7 +34176,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="B26" s="10" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>589</v>
@@ -34188,18 +34184,18 @@
     </row>
     <row r="27" spans="1:9">
       <c r="B27" s="10" t="s">
+        <v>2071</v>
+      </c>
+      <c r="I27" s="10" t="s">
         <v>2072</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>2073</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="B28" s="10" t="s">
+        <v>2073</v>
+      </c>
+      <c r="I28" s="10" t="s">
         <v>2074</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>2075</v>
       </c>
     </row>
   </sheetData>
@@ -34300,7 +34296,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -34449,7 +34445,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -34509,10 +34505,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
     </row>
   </sheetData>
@@ -34601,7 +34597,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -34609,7 +34605,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -34617,7 +34613,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -34683,7 +34679,7 @@
         <v>512</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -34770,7 +34766,7 @@
         <v>368</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -34828,7 +34824,7 @@
         <v>368</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -34865,7 +34861,7 @@
         <v>1194</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -34881,7 +34877,7 @@
         <v>1409</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -34889,7 +34885,7 @@
         <v>1766</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -34897,7 +34893,7 @@
         <v>1770</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -34905,7 +34901,7 @@
         <v>1772</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -34986,7 +34982,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -35002,7 +34998,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -35010,7 +35006,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -35229,7 +35225,7 @@
         <v>368</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -35242,7 +35238,7 @@
         <v>1454</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -35258,7 +35254,7 @@
         <v>1460</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -35266,7 +35262,7 @@
         <v>1463</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -35274,7 +35270,7 @@
         <v>1465</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -35284,7 +35280,7 @@
     </row>
     <row r="30" spans="1:9">
       <c r="B30" s="10" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="I30" s="10" t="s">
         <v>875</v>
@@ -35292,7 +35288,7 @@
     </row>
     <row r="31" spans="1:9">
       <c r="B31" s="10" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="I31" s="10" t="s">
         <v>875</v>
@@ -35300,7 +35296,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="B32" s="10" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>875</v>
@@ -35359,7 +35355,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -35407,7 +35403,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -35415,7 +35411,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -35548,7 +35544,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -35556,7 +35552,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -35616,10 +35612,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
     </row>
   </sheetData>
@@ -35716,7 +35712,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -38430,7 +38426,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -38547,7 +38543,7 @@
         <v>1964</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -38555,7 +38551,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -38579,7 +38575,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -38587,7 +38583,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -38742,7 +38738,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -38758,7 +38754,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -38766,7 +38762,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -38892,10 +38888,10 @@
     </row>
     <row r="22" spans="1:9">
       <c r="B22" s="10" t="s">
+        <v>2111</v>
+      </c>
+      <c r="I22" s="10" t="s">
         <v>2112</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>2113</v>
       </c>
     </row>
   </sheetData>
@@ -39053,10 +39049,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
   </sheetData>
@@ -39213,10 +39209,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
     </row>
   </sheetData>
@@ -39522,10 +39518,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
     </row>
   </sheetData>
@@ -39574,7 +39570,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -39622,7 +39618,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -39630,7 +39626,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -39756,7 +39752,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="B23" s="10" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>614</v>
@@ -39764,7 +39760,7 @@
     </row>
     <row r="24" spans="1:9">
       <c r="B24" s="10" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>614</v>
@@ -39772,7 +39768,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="B25" s="10" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>614</v>
@@ -39827,7 +39823,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -39935,10 +39931,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
     </row>
   </sheetData>
@@ -39987,7 +39983,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -40035,7 +40031,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -42717,7 +42713,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -42733,7 +42729,7 @@
         <v>1964</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -42741,7 +42737,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -42765,7 +42761,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -42839,7 +42835,7 @@
         <v>368</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -42868,7 +42864,7 @@
         <v>368</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -42897,7 +42893,7 @@
         <v>368</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -42910,7 +42906,7 @@
         <v>1409</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -42926,7 +42922,7 @@
         <v>1416</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -42952,7 +42948,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="B27" s="10" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>829</v>
@@ -42960,10 +42956,10 @@
     </row>
     <row r="28" spans="1:9">
       <c r="B28" s="10" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
     </row>
   </sheetData>
@@ -43016,7 +43012,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -43040,7 +43036,7 @@
         <v>1965</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -43064,7 +43060,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -43138,7 +43134,7 @@
         <v>368</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -43167,7 +43163,7 @@
         <v>368</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -43196,7 +43192,7 @@
         <v>368</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -43208,8 +43204,8 @@
       <c r="A19" t="s">
         <v>1392</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>1393</v>
+      <c r="B19" s="12" t="s">
+        <v>2136</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -43257,7 +43253,7 @@
         <v>1409</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -43315,10 +43311,10 @@
     </row>
     <row r="35" spans="2:9">
       <c r="B35" s="10" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
     </row>
   </sheetData>
@@ -43331,6 +43327,7 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C1" location="Main!A1" display="back to main"/>
+    <hyperlink ref="B19" location="T1034!A1" display="Use a brute force attack instead (T1034)"/>
     <hyperlink ref="B25" location="T1037!A1" display="Attempt to obtain password/passcode from the device owner (T1037)"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -43373,7 +43370,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -43522,7 +43519,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -43570,7 +43567,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -43671,7 +43668,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -43719,7 +43716,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -43779,7 +43776,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2144</v>
@@ -43831,7 +43828,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -44000,7 +43997,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -44237,7 +44234,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -44345,7 +44342,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2156</v>
@@ -50283,7 +50280,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -50291,7 +50288,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -50631,7 +50628,7 @@
         <v>1968</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -50639,7 +50636,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -51080,7 +51077,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="B20" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>2183</v>
@@ -51799,7 +51796,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="B20" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>2203</v>
@@ -51969,7 +51966,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2204</v>
@@ -52021,7 +52018,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -52374,7 +52371,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -52482,7 +52479,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2213</v>
@@ -56916,7 +56913,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2219</v>
@@ -56968,7 +56965,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -57076,7 +57073,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2221</v>
@@ -57919,7 +57916,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -58881,7 +58878,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2256</v>
@@ -60207,7 +60204,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2287</v>
@@ -60367,7 +60364,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2288</v>
@@ -60527,7 +60524,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2291</v>
@@ -61011,7 +61008,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -63150,7 +63147,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -64074,7 +64071,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2339</v>
@@ -64234,7 +64231,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2341</v>
@@ -64394,7 +64391,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2342</v>
@@ -64554,7 +64551,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2343</v>
@@ -64803,7 +64800,7 @@
         <v>1970</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2002</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -64811,7 +64808,7 @@
         <v>1972</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -64877,7 +64874,7 @@
         <v>368</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -65032,23 +65029,23 @@
     </row>
     <row r="27" spans="1:9">
       <c r="B27" s="10" t="s">
+        <v>2004</v>
+      </c>
+      <c r="I27" s="10" t="s">
         <v>2005</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>2006</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="B28" s="10" t="s">
+        <v>2006</v>
+      </c>
+      <c r="I28" s="10" t="s">
         <v>2007</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>2008</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="B29" s="10" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>577</v>
@@ -65056,15 +65053,15 @@
     </row>
     <row r="30" spans="1:9">
       <c r="B30" s="10" t="s">
+        <v>2009</v>
+      </c>
+      <c r="I30" s="10" t="s">
         <v>2010</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>2011</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="B31" s="10" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="I31" s="10" t="s">
         <v>1381</v>
@@ -65072,7 +65069,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="B32" s="10" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>1381</v>
@@ -65080,7 +65077,7 @@
     </row>
     <row r="33" spans="2:9">
       <c r="B33" s="10" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="I33" s="10" t="s">
         <v>1381</v>
@@ -65088,7 +65085,7 @@
     </row>
     <row r="34" spans="2:9">
       <c r="B34" s="10" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="I34" s="10" t="s">
         <v>1384</v>
@@ -65096,15 +65093,15 @@
     </row>
     <row r="35" spans="2:9">
       <c r="B35" s="10" t="s">
+        <v>2015</v>
+      </c>
+      <c r="I35" s="10" t="s">
         <v>2016</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>2017</v>
       </c>
     </row>
     <row r="36" spans="2:9">
       <c r="B36" s="10" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="I36" s="10" t="s">
         <v>1384</v>
@@ -65112,10 +65109,10 @@
     </row>
     <row r="37" spans="2:9">
       <c r="B37" s="10" t="s">
+        <v>2018</v>
+      </c>
+      <c r="I37" s="10" t="s">
         <v>2019</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>2020</v>
       </c>
     </row>
   </sheetData>
@@ -65283,7 +65280,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2345</v>
@@ -65443,7 +65440,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2346</v>
@@ -66227,7 +66224,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2369</v>
@@ -66387,7 +66384,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2370</v>
@@ -66439,7 +66436,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -66647,7 +66644,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -66944,7 +66941,7 @@
         <v>1961</v>
       </c>
       <c r="B3" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="4" spans="1:10">

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13464,7 +13464,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-05T19:10:06.448943+00:00</t>
+    <t>2026-03-05T19:14:33.221174+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13464,7 +13464,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-05T19:14:33.221174+00:00</t>
+    <t>2026-03-05T19:20:56.352355+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13464,7 +13464,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-05T19:20:56.352355+00:00</t>
+    <t>2026-03-05T19:31:34.482953+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13464,7 +13464,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-05T19:31:34.482953+00:00</t>
+    <t>2026-03-06T11:46:25.985890+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13464,7 +13464,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-06T11:46:25.985890+00:00</t>
+    <t>2026-03-06T14:17:00.568089+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13464,7 +13464,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-06T14:17:00.568089+00:00</t>
+    <t>2026-03-06T14:20:50.762437+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13464,7 +13464,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-06T14:20:50.762437+00:00</t>
+    <t>2026-03-06T14:44:56.438901+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13464,7 +13464,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-06T14:44:56.438901+00:00</t>
+    <t>2026-03-06T15:10:44.574978+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13464,7 +13464,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-06T15:10:44.574978+00:00</t>
+    <t>2026-03-09T20:53:49.225920+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13464,7 +13464,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-09T20:53:49.225920+00:00</t>
+    <t>2026-03-09T21:57:40.679952+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13464,7 +13464,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-09T21:57:40.679952+00:00</t>
+    <t>2026-03-09T22:09:55.650616+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13464,7 +13464,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-09T22:09:55.650616+00:00</t>
+    <t>2026-03-09T22:16:50.245688+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>
@@ -13541,37 +13541,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="FFF0FAF5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4CCCC"/>
+        <fgColor rgb="FFFDF3F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE5CD"/>
+        <fgColor rgb="FFFDF8EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE4F0E0"/>
+        <fgColor rgb="FFF4FBF8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7DBDB"/>
+        <fgColor rgb="FFFDF6F5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCECDC"/>
+        <fgColor rgb="FFFDFAF3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13464,7 +13464,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-09T22:16:50.245688+00:00</t>
+    <t>2026-03-09T22:53:44.133421+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13464,7 +13464,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-09T22:53:44.133421+00:00</t>
+    <t>2026-03-10T12:18:23.933624+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13464,7 +13464,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-10T12:18:23.933624+00:00</t>
+    <t>2026-03-10T13:07:11.429138+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13538,7 +13538,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-11T23:46:11.490123+00:00</t>
+    <t>2026-03-12T13:47:48.111069+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>
